--- a/Output Files DeepSeek V4 Flash/position_bias/position_bias_summary_deepseek.xlsx
+++ b/Output Files DeepSeek V4 Flash/position_bias/position_bias_summary_deepseek.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,790 +1267,6 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2342</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.3279</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0288</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.2855</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.3573</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.09370000000000001</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-3.26</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.4564</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5446</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0227</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.5077</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5692</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.0882</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.7795</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.8154</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.0149</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.7949000000000001</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.8359</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.0359</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.2564</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.3538</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.0265</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.3128</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.3769</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.0974</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>-0.0476</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.0419</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.0407</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.09520000000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.0895</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.3714</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.3286</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.3714</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="K23" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.5857</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.6629</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0344</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.6143</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.0772</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.0571</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.0371</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.09420000000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.2513</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.4174</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0638</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.3231</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.4974</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-0.1661</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.3846</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.7015</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0649</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.6308</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.7846</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-0.3169</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-4.88</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.8769</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.9015</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.8615</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-0.0246</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="K28" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.4661</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.3769</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.5308</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.1661</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.5444</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.5645</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0277</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.5222</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.5889</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-0.0201</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.6333</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.6266</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.6833</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="K31" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.0204</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.8833</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.9333</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.6017</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.0199</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-0.0267</v>
-      </c>
-      <c r="J33" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="K33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>5</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
